--- a/results/Int All Data 0.1/Rando_5_permute.xlsx
+++ b/results/Int All Data 0.1/Rando_5_permute.xlsx
@@ -440,27 +440,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8656299840510366</v>
+        <v>0.8884142173615858</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8574561403508771</v>
+        <v>0.8900091136933241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8343586238323081</v>
+        <v>0.8906356801093643</v>
       </c>
     </row>
     <row r="5">
@@ -470,1517 +470,1517 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8408521303258145</v>
+        <v>0.8956482114376851</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8411654135338347</v>
+        <v>0.8878161312371839</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.8954203691045797</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8464912280701754</v>
+        <v>0.8934837092731829</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8593358395989975</v>
+        <v>0.8934837092731829</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8624686716791981</v>
+        <v>0.8927717019822283</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8594212804739121</v>
+        <v>0.8916040100250626</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8594212804739121</v>
+        <v>0.9069548872180451</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8616712235133288</v>
+        <v>0.8943381180223285</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8604180906812486</v>
+        <v>0.8871610845295056</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8604180906812486</v>
+        <v>0.8913761676919572</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8620129870129871</v>
+        <v>0.8928286625655046</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8738892686261107</v>
+        <v>0.8870186830713147</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8742025518341308</v>
+        <v>0.8870186830713147</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8726076555023923</v>
+        <v>0.8889553429027113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8650034176349966</v>
+        <v>0.8877591706539074</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8650888585099111</v>
+        <v>0.8851389838231943</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8644338118022328</v>
+        <v>0.889980633401686</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8661711095921623</v>
+        <v>0.8843700159489634</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.873775347459558</v>
+        <v>0.8856231487810435</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8735475051264525</v>
+        <v>0.871639325586694</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8722943722943723</v>
+        <v>0.871639325586694</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8701013898382319</v>
+        <v>0.8721234905445432</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8698735475051265</v>
+        <v>0.861244019138756</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8710412394622922</v>
+        <v>0.8733481430849852</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8691900205058101</v>
+        <v>0.8834871269081795</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8705285942128047</v>
+        <v>0.8863066757803599</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8727215766689451</v>
+        <v>0.8667976760082023</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8725791752107541</v>
+        <v>0.9014297106402369</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8682216905901117</v>
+        <v>0.8956766917293233</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.867509683299157</v>
+        <v>0.9096035543403964</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8509341535657325</v>
+        <v>0.929710640236956</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8458361813624972</v>
+        <v>0.9298815219867851</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8417065390749601</v>
+        <v>0.9288277511961722</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8417065390749601</v>
+        <v>0.9295967190704033</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8480861244019139</v>
+        <v>0.9266917293233083</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.850848712690818</v>
+        <v>0.9291979949874687</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8464342674868991</v>
+        <v>0.9330997949419002</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8464342674868991</v>
+        <v>0.9323877876509455</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8464342674868991</v>
+        <v>0.9332421964000911</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8519594440647071</v>
+        <v>0.9342674868990659</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8454374572795625</v>
+        <v>0.9342674868990659</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8353269537480064</v>
+        <v>0.9340396445659603</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.836038961038961</v>
+        <v>0.9315618591934381</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.836038961038961</v>
+        <v>0.9315618591934381</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8247607655502392</v>
+        <v>0.9294827979038505</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8296308954203691</v>
+        <v>0.929397357028936</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8325643654591023</v>
+        <v>0.9338972431077694</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8338174982911826</v>
+        <v>0.9345522898154477</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8410230120756437</v>
+        <v>0.9183470038733197</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8396844383686488</v>
+        <v>0.9195431761221236</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8453235361130098</v>
+        <v>0.9195431761221236</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8050524037366142</v>
+        <v>0.9167236272499431</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8157609933925724</v>
+        <v>0.930479608111187</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8123148781043519</v>
+        <v>0.930479608111187</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.812941444520392</v>
+        <v>0.9122807017543859</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8306561859193438</v>
+        <v>0.9101731601731602</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8218842560947823</v>
+        <v>0.9101731601731602</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.813112326270221</v>
+        <v>0.8922020961494646</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8096662109820005</v>
+        <v>0.8980975165185692</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8107484620642516</v>
+        <v>0.8971576668945089</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7760879471405787</v>
+        <v>0.9046764638869902</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8003531556163135</v>
+        <v>0.9012018683071314</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7968500797448166</v>
+        <v>0.8899236728184097</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7981032125768968</v>
+        <v>0.8863921166552746</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7984164957849169</v>
+        <v>0.8873034859876965</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7984164957849169</v>
+        <v>0.8648325358851675</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7928628389154705</v>
+        <v>0.8690760993392572</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7800182273866485</v>
+        <v>0.8683640920483027</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7641262246525404</v>
+        <v>0.8683640920483027</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7600250626566416</v>
+        <v>0.8661426293005241</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7664616085668717</v>
+        <v>0.8758828890407837</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7742082478924583</v>
+        <v>0.877136021872864</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7679995443153338</v>
+        <v>0.8744019138755981</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7302631578947368</v>
+        <v>0.8795283663704716</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.75580997949419</v>
+        <v>0.8655445431761222</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7346206425153794</v>
+        <v>0.865231259968102</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7425381635907952</v>
+        <v>0.8710127591706539</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7535885167464116</v>
+        <v>0.9066131237183869</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7322852586010481</v>
+        <v>0.9078662565504672</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7375541125541125</v>
+        <v>0.8804397357028936</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7192697653223969</v>
+        <v>0.8785885167464115</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7245955798587378</v>
+        <v>0.8790157211209843</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7124344953292321</v>
+        <v>0.8533264980633402</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7140009113693324</v>
+        <v>0.8575415812257918</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7140009113693324</v>
+        <v>0.8389439507860561</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6839257233994076</v>
+        <v>0.8351275917065391</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6905046707678286</v>
+        <v>0.8339883800410117</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6987924356345409</v>
+        <v>0.8468329915698336</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6987924356345409</v>
+        <v>0.8305992253360674</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6903053087263613</v>
+        <v>0.8308555479608111</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6622237411711096</v>
+        <v>0.8308555479608111</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6622237411711096</v>
+        <v>0.8286625655046708</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6615971747550695</v>
+        <v>0.8299726589200274</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6597174755069493</v>
+        <v>0.8351275917065391</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6449077238550922</v>
+        <v>0.8198336750968329</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5828776486671223</v>
+        <v>0.8289188881294145</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5838174982911825</v>
+        <v>0.8041125541125541</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5743620414673046</v>
+        <v>0.8041125541125541</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5743050808840282</v>
+        <v>0.8041125541125541</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5711722488038278</v>
+        <v>0.8029733424470267</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5700330371383003</v>
+        <v>0.7542435634540898</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5700330371383003</v>
+        <v>0.7710184552289816</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5735361130097972</v>
+        <v>0.7715026201868307</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5642800182273866</v>
+        <v>0.7779106858054227</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5711722488038278</v>
+        <v>0.7873661426293005</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5752734107997266</v>
+        <v>0.7832649806334017</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5721975393028025</v>
+        <v>0.7669457735247209</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5647357028935976</v>
+        <v>0.7794201412622466</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5603212576896788</v>
+        <v>0.7794201412622466</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5521758942811574</v>
+        <v>0.7491171109592163</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5204203691045796</v>
+        <v>0.7475222146274778</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5080599225336068</v>
+        <v>0.6163989519252677</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5042150831624516</v>
+        <v>0.6151173388015493</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5024208247892459</v>
+        <v>0.6151173388015493</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5027341079972659</v>
+        <v>0.5992822966507177</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5043574846206426</v>
+        <v>0.5897698792435634</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5035885167464115</v>
+        <v>0.5939280018227386</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5018796992481203</v>
+        <v>0.6070574162679426</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5018796992481203</v>
+        <v>0.6150318979266347</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5018796992481203</v>
+        <v>0.6136933242196401</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5015664160401002</v>
+        <v>0.4665071770334928</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5018796992481203</v>
+        <v>0.4709785828206881</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5</v>
+        <v>0.4615516062884484</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5</v>
+        <v>0.4629471405787196</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5</v>
+        <v>0.4839940760993393</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5</v>
+        <v>0.4888072453861927</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.4885224424698109</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.48869332421964</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.4973228525860105</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.4833675096832992</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5</v>
+        <v>0.4833675096832992</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.50031328320802</v>
+        <v>0.4057587149692413</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.50031328320802</v>
+        <v>0.4443210298473457</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.50031328320802</v>
+        <v>0.4411312371838688</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5009398496240601</v>
+        <v>0.4763613579403053</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5015664160401002</v>
+        <v>0.446058327637275</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5015664160401002</v>
+        <v>0.4435235816814764</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5012531328320802</v>
+        <v>0.4591592617908407</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5006265664160401</v>
+        <v>0.461950330371383</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5006265664160401</v>
+        <v>0.4396502620186831</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5006265664160401</v>
+        <v>0.4524094326725906</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5006265664160401</v>
+        <v>0.4449475962633857</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5006265664160401</v>
+        <v>0.4452608794714057</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5006265664160401</v>
+        <v>0.4395933014354066</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5006265664160401</v>
+        <v>0.4406755525176578</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5006265664160401</v>
+        <v>0.4516119845067214</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5006265664160401</v>
+        <v>0.470807701070859</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4990316700843017</v>
+        <v>0.4779562542720437</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4999145591250854</v>
+        <v>0.4779562542720437</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.50031328320802</v>
+        <v>0.4793517885623149</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.4884370015948963</v>
       </c>
     </row>
   </sheetData>
